--- a/outputs_xlsx_solution/test33.4-wide-NR-4.xlsx
+++ b/outputs_xlsx_solution/test33.4-wide-NR-4.xlsx
@@ -80,6 +80,9 @@
     <t>EX</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>RS Stall</t>
   </si>
   <si>
@@ -207,6 +210,9 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -1029,7 +1035,7 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -1049,13 +1055,13 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -1075,16 +1081,16 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" t="s">
         <v>15</v>
       </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
       <c r="H4" t="s">
         <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -1104,16 +1110,16 @@
         <v>9</v>
       </c>
       <c r="G5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" t="s">
         <v>15</v>
       </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
       <c r="I5" t="s">
         <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -1133,16 +1139,16 @@
         <v>9</v>
       </c>
       <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" t="s">
         <v>15</v>
       </c>
-      <c r="I6" t="s">
-        <v>14</v>
-      </c>
       <c r="J6" t="s">
         <v>14</v>
       </c>
       <c r="K6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -1162,16 +1168,16 @@
         <v>9</v>
       </c>
       <c r="I7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" t="s">
         <v>15</v>
       </c>
-      <c r="J7" t="s">
-        <v>14</v>
-      </c>
       <c r="K7" t="s">
         <v>14</v>
       </c>
       <c r="L7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -1194,10 +1200,10 @@
         <v>14</v>
       </c>
       <c r="K8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -1217,13 +1223,13 @@
         <v>9</v>
       </c>
       <c r="J9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K9" t="s">
         <v>14</v>
       </c>
       <c r="L9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -1234,7 +1240,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
@@ -1243,16 +1249,16 @@
         <v>9</v>
       </c>
       <c r="J10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L10" t="s">
         <v>14</v>
       </c>
       <c r="M10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
@@ -1263,7 +1269,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
@@ -1272,7 +1278,7 @@
         <v>9</v>
       </c>
       <c r="K11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L11" t="s">
         <v>14</v>
@@ -1284,7 +1290,7 @@
         <v>14</v>
       </c>
       <c r="O11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -1295,7 +1301,7 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
         <v>5</v>
@@ -1304,7 +1310,7 @@
         <v>9</v>
       </c>
       <c r="L12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O12" t="s">
         <v>14</v>
@@ -1316,7 +1322,7 @@
         <v>14</v>
       </c>
       <c r="R12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -1327,7 +1333,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F13" t="s">
         <v>5</v>
@@ -1336,7 +1342,7 @@
         <v>9</v>
       </c>
       <c r="L13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R13" t="s">
         <v>14</v>
@@ -1351,7 +1357,7 @@
         <v>14</v>
       </c>
       <c r="V13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
@@ -1362,7 +1368,7 @@
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G14" t="s">
         <v>5</v>
@@ -1371,7 +1377,7 @@
         <v>9</v>
       </c>
       <c r="L14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M14" t="s">
         <v>14</v>
@@ -1386,10 +1392,10 @@
         <v>14</v>
       </c>
       <c r="Q14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -1400,7 +1406,7 @@
         <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G15" t="s">
         <v>5</v>
@@ -1409,10 +1415,10 @@
         <v>9</v>
       </c>
       <c r="M15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O15" t="s">
         <v>14</v>
@@ -1433,10 +1439,10 @@
         <v>14</v>
       </c>
       <c r="U15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
@@ -1447,7 +1453,7 @@
         <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G16" t="s">
         <v>5</v>
@@ -1456,22 +1462,22 @@
         <v>9</v>
       </c>
       <c r="O16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R16" t="s">
         <v>14</v>
       </c>
       <c r="S16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -1491,22 +1497,22 @@
         <v>9</v>
       </c>
       <c r="R17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="S17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="V17" t="s">
         <v>14</v>
       </c>
       <c r="W17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -1517,7 +1523,7 @@
         <v>64</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H18" t="s">
         <v>5</v>
@@ -1529,7 +1535,7 @@
         <v>14</v>
       </c>
       <c r="W18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1540,7 +1546,7 @@
         <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H19" t="s">
         <v>5</v>
@@ -1549,13 +1555,13 @@
         <v>9</v>
       </c>
       <c r="V19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W19" t="s">
         <v>14</v>
       </c>
       <c r="X19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -1566,7 +1572,7 @@
         <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H20" t="s">
         <v>5</v>
@@ -1575,7 +1581,7 @@
         <v>9</v>
       </c>
       <c r="V20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X20" t="s">
         <v>14</v>
@@ -1590,7 +1596,7 @@
         <v>14</v>
       </c>
       <c r="AB20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -1601,7 +1607,7 @@
         <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H21" t="s">
         <v>5</v>
@@ -1610,7 +1616,7 @@
         <v>9</v>
       </c>
       <c r="W21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AB21" t="s">
         <v>14</v>
@@ -1622,7 +1628,7 @@
         <v>14</v>
       </c>
       <c r="AE21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
@@ -1633,7 +1639,7 @@
         <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I22" t="s">
         <v>5</v>
@@ -1642,13 +1648,13 @@
         <v>9</v>
       </c>
       <c r="W22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AE22" t="s">
         <v>14</v>
       </c>
       <c r="AF22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
@@ -1659,7 +1665,7 @@
         <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I23" t="s">
         <v>5</v>
@@ -1668,16 +1674,16 @@
         <v>9</v>
       </c>
       <c r="W23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X23" t="s">
         <v>14</v>
       </c>
       <c r="Y23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24">
@@ -1688,7 +1694,7 @@
         <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I24" t="s">
         <v>5</v>
@@ -1697,28 +1703,28 @@
         <v>9</v>
       </c>
       <c r="X24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Y24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Z24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AA24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AB24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AC24" t="s">
         <v>14</v>
       </c>
       <c r="AD24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -1729,7 +1735,7 @@
         <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AD25" t="s">
         <v>5</v>
@@ -1741,7 +1747,7 @@
         <v>14</v>
       </c>
       <c r="AG25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26">
@@ -1752,7 +1758,7 @@
         <v>72</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AD26" t="s">
         <v>5</v>
@@ -1761,7 +1767,7 @@
         <v>9</v>
       </c>
       <c r="AF26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AG26" t="s">
         <v>14</v>
@@ -1776,7 +1782,7 @@
         <v>14</v>
       </c>
       <c r="AK26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
@@ -1787,7 +1793,7 @@
         <v>76</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AD27" t="s">
         <v>5</v>
@@ -1796,7 +1802,7 @@
         <v>9</v>
       </c>
       <c r="AF27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AK27" t="s">
         <v>14</v>
@@ -1808,7 +1814,7 @@
         <v>14</v>
       </c>
       <c r="AN27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28">
@@ -1819,7 +1825,7 @@
         <v>80</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AD28" t="s">
         <v>5</v>
@@ -1828,13 +1834,13 @@
         <v>9</v>
       </c>
       <c r="AF28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AN28" t="s">
         <v>14</v>
       </c>
       <c r="AO28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
@@ -1845,7 +1851,7 @@
         <v>84</v>
       </c>
       <c r="C29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AE29" t="s">
         <v>5</v>
@@ -1857,10 +1863,10 @@
         <v>14</v>
       </c>
       <c r="AH29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30">
@@ -1871,7 +1877,7 @@
         <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AE30" t="s">
         <v>5</v>
@@ -1880,28 +1886,28 @@
         <v>9</v>
       </c>
       <c r="AG30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AH30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AI30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AJ30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AK30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AL30" t="s">
         <v>14</v>
       </c>
       <c r="AM30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31">
@@ -1912,7 +1918,7 @@
         <v>68</v>
       </c>
       <c r="C31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF31" t="s">
         <v>5</v>
@@ -1921,22 +1927,22 @@
         <v>9</v>
       </c>
       <c r="AK31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AL31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AM31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AN31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO31" t="s">
         <v>14</v>
       </c>
       <c r="AP31" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32">
@@ -1947,7 +1953,7 @@
         <v>72</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF32" t="s">
         <v>5</v>
@@ -1956,10 +1962,10 @@
         <v>9</v>
       </c>
       <c r="AN32" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AO32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AP32" t="s">
         <v>14</v>
@@ -1974,7 +1980,7 @@
         <v>14</v>
       </c>
       <c r="AT32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33">
@@ -1985,7 +1991,7 @@
         <v>76</v>
       </c>
       <c r="C33" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF33" t="s">
         <v>5</v>
@@ -1994,7 +2000,7 @@
         <v>9</v>
       </c>
       <c r="AO33" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AT33" t="s">
         <v>14</v>
@@ -2006,7 +2012,7 @@
         <v>14</v>
       </c>
       <c r="AW33" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34">
@@ -2017,7 +2023,7 @@
         <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF34" t="s">
         <v>5</v>
@@ -2026,13 +2032,13 @@
         <v>9</v>
       </c>
       <c r="AO34" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AW34" t="s">
         <v>14</v>
       </c>
       <c r="AX34" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35">
@@ -2043,7 +2049,7 @@
         <v>84</v>
       </c>
       <c r="C35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG35" t="s">
         <v>5</v>
@@ -2052,16 +2058,16 @@
         <v>9</v>
       </c>
       <c r="AO35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AP35" t="s">
         <v>14</v>
       </c>
       <c r="AQ35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36">
@@ -2072,7 +2078,7 @@
         <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AG36" t="s">
         <v>5</v>
@@ -2081,28 +2087,28 @@
         <v>9</v>
       </c>
       <c r="AP36" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AQ36" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AR36" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AS36" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AT36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AU36" t="s">
         <v>14</v>
       </c>
       <c r="AV36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37">
@@ -2113,7 +2119,7 @@
         <v>92</v>
       </c>
       <c r="C37" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AV37" t="s">
         <v>5</v>
@@ -2131,7 +2137,7 @@
         <v>14</v>
       </c>
       <c r="BA37" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38">
@@ -2142,7 +2148,7 @@
         <v>96</v>
       </c>
       <c r="C38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AV38" t="s">
         <v>5</v>
@@ -2151,7 +2157,7 @@
         <v>9</v>
       </c>
       <c r="AX38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BA38" t="s">
         <v>14</v>
@@ -2163,7 +2169,7 @@
         <v>14</v>
       </c>
       <c r="BD38" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39">
@@ -2174,7 +2180,7 @@
         <v>100</v>
       </c>
       <c r="C39" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AV39" t="s">
         <v>5</v>
@@ -2186,10 +2192,10 @@
         <v>14</v>
       </c>
       <c r="AY39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40">
@@ -2200,7 +2206,7 @@
         <v>104</v>
       </c>
       <c r="C40" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AV40" t="s">
         <v>5</v>
@@ -2209,10 +2215,10 @@
         <v>14</v>
       </c>
       <c r="AY40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD40" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41">
@@ -2223,7 +2229,7 @@
         <v>36</v>
       </c>
       <c r="C41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW41" t="s">
         <v>5</v>
@@ -2232,13 +2238,13 @@
         <v>9</v>
       </c>
       <c r="AY41" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AZ41" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BA41" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB41" t="s">
         <v>14</v>
@@ -2250,7 +2256,7 @@
         <v>14</v>
       </c>
       <c r="BE41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42">
@@ -2261,7 +2267,7 @@
         <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW42" t="s">
         <v>5</v>
@@ -2270,16 +2276,16 @@
         <v>9</v>
       </c>
       <c r="BA42" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BB42" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BC42" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BD42" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BE42" t="s">
         <v>14</v>
@@ -2291,7 +2297,7 @@
         <v>14</v>
       </c>
       <c r="BH42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43">
@@ -2302,7 +2308,7 @@
         <v>44</v>
       </c>
       <c r="C43" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW43" t="s">
         <v>5</v>
@@ -2311,7 +2317,7 @@
         <v>9</v>
       </c>
       <c r="BD43" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BH43" t="s">
         <v>14</v>
@@ -2326,7 +2332,7 @@
         <v>14</v>
       </c>
       <c r="BL43" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44">
@@ -2337,7 +2343,7 @@
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW44" t="s">
         <v>5</v>
@@ -2358,10 +2364,10 @@
         <v>14</v>
       </c>
       <c r="BH44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BL44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45">
@@ -2372,7 +2378,7 @@
         <v>52</v>
       </c>
       <c r="C45" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX45" t="s">
         <v>5</v>
@@ -2381,7 +2387,7 @@
         <v>9</v>
       </c>
       <c r="BD45" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BE45" t="s">
         <v>14</v>
@@ -2402,10 +2408,10 @@
         <v>14</v>
       </c>
       <c r="BK45" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BL45" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46">
@@ -2416,7 +2422,7 @@
         <v>56</v>
       </c>
       <c r="C46" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX46" t="s">
         <v>5</v>
@@ -2425,22 +2431,22 @@
         <v>9</v>
       </c>
       <c r="BE46" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BF46" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BG46" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BH46" t="s">
         <v>14</v>
       </c>
       <c r="BI46" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BL46" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47">
@@ -2460,22 +2466,22 @@
         <v>9</v>
       </c>
       <c r="BH47" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BI47" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BJ47" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BK47" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BL47" t="s">
         <v>14</v>
       </c>
       <c r="BM47" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48">
@@ -2486,7 +2492,7 @@
         <v>64</v>
       </c>
       <c r="C48" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX48" t="s">
         <v>5</v>
@@ -2498,7 +2504,7 @@
         <v>14</v>
       </c>
       <c r="BM48" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49">
@@ -2509,7 +2515,7 @@
         <v>68</v>
       </c>
       <c r="C49" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY49" t="s">
         <v>5</v>
@@ -2518,13 +2524,13 @@
         <v>9</v>
       </c>
       <c r="BL49" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BM49" t="s">
         <v>14</v>
       </c>
       <c r="BN49" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50">
@@ -2535,7 +2541,7 @@
         <v>72</v>
       </c>
       <c r="C50" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY50" t="s">
         <v>5</v>
@@ -2544,7 +2550,7 @@
         <v>9</v>
       </c>
       <c r="BL50" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BN50" t="s">
         <v>14</v>
@@ -2559,7 +2565,7 @@
         <v>14</v>
       </c>
       <c r="BR50" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51">
@@ -2570,7 +2576,7 @@
         <v>76</v>
       </c>
       <c r="C51" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY51" t="s">
         <v>5</v>
@@ -2579,7 +2585,7 @@
         <v>9</v>
       </c>
       <c r="BM51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BR51" t="s">
         <v>14</v>
@@ -2591,7 +2597,7 @@
         <v>14</v>
       </c>
       <c r="BU51" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52">
@@ -2602,7 +2608,7 @@
         <v>80</v>
       </c>
       <c r="C52" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY52" t="s">
         <v>5</v>
@@ -2611,13 +2617,13 @@
         <v>9</v>
       </c>
       <c r="BM52" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BU52" t="s">
         <v>14</v>
       </c>
       <c r="BV52" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53">
@@ -2628,7 +2634,7 @@
         <v>84</v>
       </c>
       <c r="C53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AZ53" t="s">
         <v>5</v>
@@ -2637,16 +2643,16 @@
         <v>9</v>
       </c>
       <c r="BM53" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BN53" t="s">
         <v>14</v>
       </c>
       <c r="BO53" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BV53" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54">
@@ -2657,7 +2663,7 @@
         <v>88</v>
       </c>
       <c r="C54" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AZ54" t="s">
         <v>5</v>
@@ -2666,28 +2672,28 @@
         <v>9</v>
       </c>
       <c r="BN54" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BO54" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BP54" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BQ54" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BR54" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BS54" t="s">
         <v>14</v>
       </c>
       <c r="BT54" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BV54" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55">
@@ -2698,7 +2704,7 @@
         <v>68</v>
       </c>
       <c r="C55" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA55" t="s">
         <v>5</v>
@@ -2707,22 +2713,22 @@
         <v>9</v>
       </c>
       <c r="BR55" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BS55" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BT55" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BU55" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BV55" t="s">
         <v>14</v>
       </c>
       <c r="BW55" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56">
@@ -2733,7 +2739,7 @@
         <v>72</v>
       </c>
       <c r="C56" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA56" t="s">
         <v>5</v>
@@ -2742,10 +2748,10 @@
         <v>9</v>
       </c>
       <c r="BU56" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BV56" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BW56" t="s">
         <v>14</v>
@@ -2760,7 +2766,7 @@
         <v>14</v>
       </c>
       <c r="CA56" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57">
@@ -2771,7 +2777,7 @@
         <v>76</v>
       </c>
       <c r="C57" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA57" t="s">
         <v>5</v>
@@ -2780,7 +2786,7 @@
         <v>9</v>
       </c>
       <c r="BV57" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CA57" t="s">
         <v>14</v>
@@ -2792,7 +2798,7 @@
         <v>14</v>
       </c>
       <c r="CD57" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58">
@@ -2803,7 +2809,7 @@
         <v>80</v>
       </c>
       <c r="C58" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA58" t="s">
         <v>5</v>
@@ -2812,13 +2818,13 @@
         <v>9</v>
       </c>
       <c r="BV58" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CD58" t="s">
         <v>14</v>
       </c>
       <c r="CE58" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59">
@@ -2829,7 +2835,7 @@
         <v>84</v>
       </c>
       <c r="C59" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BB59" t="s">
         <v>5</v>
@@ -2838,16 +2844,16 @@
         <v>9</v>
       </c>
       <c r="BV59" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BW59" t="s">
         <v>14</v>
       </c>
       <c r="BX59" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CE59" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60">
@@ -2858,7 +2864,7 @@
         <v>88</v>
       </c>
       <c r="C60" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BB60" t="s">
         <v>5</v>
@@ -2867,28 +2873,28 @@
         <v>9</v>
       </c>
       <c r="BW60" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BX60" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BY60" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BZ60" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CA60" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CB60" t="s">
         <v>14</v>
       </c>
       <c r="CC60" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CE60" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61">
@@ -2899,7 +2905,7 @@
         <v>68</v>
       </c>
       <c r="C61" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD61" t="s">
         <v>5</v>
@@ -2908,22 +2914,22 @@
         <v>9</v>
       </c>
       <c r="CA61" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CB61" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CC61" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CD61" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CE61" t="s">
         <v>14</v>
       </c>
       <c r="CF61" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62">
@@ -2934,7 +2940,7 @@
         <v>72</v>
       </c>
       <c r="C62" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD62" t="s">
         <v>5</v>
@@ -2943,10 +2949,10 @@
         <v>9</v>
       </c>
       <c r="CD62" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CE62" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CF62" t="s">
         <v>14</v>
@@ -2961,7 +2967,7 @@
         <v>14</v>
       </c>
       <c r="CJ62" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63">
@@ -2972,7 +2978,7 @@
         <v>76</v>
       </c>
       <c r="C63" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BD63" t="s">
         <v>5</v>
@@ -2981,7 +2987,7 @@
         <v>9</v>
       </c>
       <c r="CE63" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CJ63" t="s">
         <v>14</v>
@@ -2993,7 +2999,7 @@
         <v>14</v>
       </c>
       <c r="CM63" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="64">
@@ -3004,7 +3010,7 @@
         <v>80</v>
       </c>
       <c r="C64" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD64" t="s">
         <v>5</v>
@@ -3013,13 +3019,13 @@
         <v>9</v>
       </c>
       <c r="CE64" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CM64" t="s">
         <v>14</v>
       </c>
       <c r="CN64" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65">
@@ -3030,7 +3036,7 @@
         <v>84</v>
       </c>
       <c r="C65" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BE65" t="s">
         <v>5</v>
@@ -3039,16 +3045,16 @@
         <v>9</v>
       </c>
       <c r="CE65" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CF65" t="s">
         <v>14</v>
       </c>
       <c r="CG65" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CN65" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="66">
@@ -3059,7 +3065,7 @@
         <v>88</v>
       </c>
       <c r="C66" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BH66" t="s">
         <v>5</v>
@@ -3068,28 +3074,28 @@
         <v>9</v>
       </c>
       <c r="CF66" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CG66" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CH66" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CI66" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CJ66" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CK66" t="s">
         <v>14</v>
       </c>
       <c r="CL66" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CN66" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67">
@@ -3100,7 +3106,7 @@
         <v>92</v>
       </c>
       <c r="C67" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="CL67" t="s">
         <v>5</v>
@@ -3118,7 +3124,7 @@
         <v>14</v>
       </c>
       <c r="CQ67" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="68">
@@ -3129,7 +3135,7 @@
         <v>96</v>
       </c>
       <c r="C68" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="CL68" t="s">
         <v>5</v>
@@ -3138,7 +3144,7 @@
         <v>9</v>
       </c>
       <c r="CN68" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CQ68" t="s">
         <v>14</v>
@@ -3150,7 +3156,7 @@
         <v>14</v>
       </c>
       <c r="CT68" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69">
@@ -3161,7 +3167,7 @@
         <v>100</v>
       </c>
       <c r="C69" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="CL69" t="s">
         <v>5</v>
@@ -3173,10 +3179,10 @@
         <v>14</v>
       </c>
       <c r="CO69" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CT69" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70">
@@ -3187,7 +3193,7 @@
         <v>104</v>
       </c>
       <c r="C70" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="CL70" t="s">
         <v>5</v>
@@ -3199,10 +3205,10 @@
         <v>14</v>
       </c>
       <c r="CO70" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CT70" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71">
@@ -3213,7 +3219,7 @@
         <v>36</v>
       </c>
       <c r="C71" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CM71" t="s">
         <v>5</v>
@@ -3222,13 +3228,13 @@
         <v>9</v>
       </c>
       <c r="CO71" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CP71" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CQ71" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CR71" t="s">
         <v>14</v>
@@ -3240,7 +3246,7 @@
         <v>14</v>
       </c>
       <c r="CU71" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="72">
@@ -3251,7 +3257,7 @@
         <v>40</v>
       </c>
       <c r="C72" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CM72" t="s">
         <v>5</v>
@@ -3260,16 +3266,16 @@
         <v>9</v>
       </c>
       <c r="CQ72" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CR72" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CS72" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CT72" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CU72" t="s">
         <v>14</v>
@@ -3281,7 +3287,7 @@
         <v>14</v>
       </c>
       <c r="CX72" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73">
@@ -3292,7 +3298,7 @@
         <v>44</v>
       </c>
       <c r="C73" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="CM73" t="s">
         <v>5</v>
@@ -3301,7 +3307,7 @@
         <v>9</v>
       </c>
       <c r="CT73" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CX73" t="s">
         <v>14</v>
@@ -3316,7 +3322,7 @@
         <v>14</v>
       </c>
       <c r="DB73" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74">
@@ -3327,7 +3333,7 @@
         <v>48</v>
       </c>
       <c r="C74" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CM74" t="s">
         <v>5</v>
@@ -3348,10 +3354,10 @@
         <v>14</v>
       </c>
       <c r="CX74" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DB74" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="75">
@@ -3362,7 +3368,7 @@
         <v>52</v>
       </c>
       <c r="C75" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CN75" t="s">
         <v>5</v>
@@ -3371,7 +3377,7 @@
         <v>9</v>
       </c>
       <c r="CT75" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CU75" t="s">
         <v>14</v>
@@ -3392,10 +3398,10 @@
         <v>14</v>
       </c>
       <c r="DA75" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DB75" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="76">
@@ -3406,7 +3412,7 @@
         <v>56</v>
       </c>
       <c r="C76" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CN76" t="s">
         <v>5</v>
@@ -3415,22 +3421,22 @@
         <v>9</v>
       </c>
       <c r="CU76" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CV76" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CW76" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CX76" t="s">
         <v>14</v>
       </c>
       <c r="CY76" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DB76" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77">
@@ -3450,22 +3456,22 @@
         <v>9</v>
       </c>
       <c r="CX77" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CY77" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CZ77" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DA77" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DB77" t="s">
         <v>14</v>
       </c>
       <c r="DC77" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78">
@@ -3476,7 +3482,7 @@
         <v>64</v>
       </c>
       <c r="C78" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CN78" t="s">
         <v>5</v>
@@ -3488,7 +3494,7 @@
         <v>14</v>
       </c>
       <c r="DC78" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79">
@@ -3499,7 +3505,7 @@
         <v>68</v>
       </c>
       <c r="C79" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CO79" t="s">
         <v>5</v>
@@ -3508,13 +3514,13 @@
         <v>9</v>
       </c>
       <c r="DB79" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DC79" t="s">
         <v>14</v>
       </c>
       <c r="DD79" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="80">
@@ -3525,7 +3531,7 @@
         <v>72</v>
       </c>
       <c r="C80" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CO80" t="s">
         <v>5</v>
@@ -3534,7 +3540,7 @@
         <v>9</v>
       </c>
       <c r="DB80" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="DD80" t="s">
         <v>14</v>
@@ -3549,7 +3555,7 @@
         <v>14</v>
       </c>
       <c r="DH80" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81">
@@ -3560,7 +3566,7 @@
         <v>76</v>
       </c>
       <c r="C81" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CO81" t="s">
         <v>5</v>
@@ -3569,7 +3575,7 @@
         <v>9</v>
       </c>
       <c r="DC81" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="DH81" t="s">
         <v>14</v>
@@ -3581,7 +3587,7 @@
         <v>14</v>
       </c>
       <c r="DK81" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82">
@@ -3592,7 +3598,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CO82" t="s">
         <v>5</v>
@@ -3601,13 +3607,13 @@
         <v>9</v>
       </c>
       <c r="DC82" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="DK82" t="s">
         <v>14</v>
       </c>
       <c r="DL82" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83">
@@ -3618,7 +3624,7 @@
         <v>84</v>
       </c>
       <c r="C83" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="CP83" t="s">
         <v>5</v>
@@ -3627,16 +3633,16 @@
         <v>9</v>
       </c>
       <c r="DC83" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DD83" t="s">
         <v>14</v>
       </c>
       <c r="DE83" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DL83" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="84">
@@ -3647,7 +3653,7 @@
         <v>88</v>
       </c>
       <c r="C84" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="CP84" t="s">
         <v>5</v>
@@ -3656,28 +3662,28 @@
         <v>9</v>
       </c>
       <c r="DD84" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DE84" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DF84" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DG84" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DH84" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="DI84" t="s">
         <v>14</v>
       </c>
       <c r="DJ84" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DL84" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="85">
@@ -3688,7 +3694,7 @@
         <v>68</v>
       </c>
       <c r="C85" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CQ85" t="s">
         <v>5</v>
@@ -3697,22 +3703,22 @@
         <v>9</v>
       </c>
       <c r="DH85" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DI85" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DJ85" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DK85" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DL85" t="s">
         <v>14</v>
       </c>
       <c r="DM85" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="86">
@@ -3723,7 +3729,7 @@
         <v>72</v>
       </c>
       <c r="C86" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CQ86" t="s">
         <v>5</v>
@@ -3732,10 +3738,10 @@
         <v>9</v>
       </c>
       <c r="DK86" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DL86" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="DM86" t="s">
         <v>14</v>
@@ -3750,7 +3756,7 @@
         <v>14</v>
       </c>
       <c r="DQ86" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87">
@@ -3761,7 +3767,7 @@
         <v>76</v>
       </c>
       <c r="C87" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CQ87" t="s">
         <v>5</v>
@@ -3770,7 +3776,7 @@
         <v>9</v>
       </c>
       <c r="DL87" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="DQ87" t="s">
         <v>14</v>
@@ -3782,7 +3788,7 @@
         <v>14</v>
       </c>
       <c r="DT87" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="88">
@@ -3793,7 +3799,7 @@
         <v>80</v>
       </c>
       <c r="C88" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CQ88" t="s">
         <v>5</v>
@@ -3802,13 +3808,13 @@
         <v>9</v>
       </c>
       <c r="DL88" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="DT88" t="s">
         <v>14</v>
       </c>
       <c r="DU88" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="89">
@@ -3819,7 +3825,7 @@
         <v>84</v>
       </c>
       <c r="C89" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="CR89" t="s">
         <v>5</v>
@@ -3828,16 +3834,16 @@
         <v>9</v>
       </c>
       <c r="DL89" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DM89" t="s">
         <v>14</v>
       </c>
       <c r="DN89" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DU89" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="90">
@@ -3848,7 +3854,7 @@
         <v>88</v>
       </c>
       <c r="C90" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="CR90" t="s">
         <v>5</v>
@@ -3857,28 +3863,28 @@
         <v>9</v>
       </c>
       <c r="DM90" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DN90" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DO90" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DP90" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DQ90" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="DR90" t="s">
         <v>14</v>
       </c>
       <c r="DS90" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DU90" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="91">
@@ -3889,7 +3895,7 @@
         <v>68</v>
       </c>
       <c r="C91" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CT91" t="s">
         <v>5</v>
@@ -3898,22 +3904,22 @@
         <v>9</v>
       </c>
       <c r="DQ91" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DR91" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DS91" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DT91" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DU91" t="s">
         <v>14</v>
       </c>
       <c r="DV91" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="92">
@@ -3924,7 +3930,7 @@
         <v>72</v>
       </c>
       <c r="C92" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CT92" t="s">
         <v>5</v>
@@ -3933,10 +3939,10 @@
         <v>9</v>
       </c>
       <c r="DT92" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DU92" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="DV92" t="s">
         <v>14</v>
@@ -3951,7 +3957,7 @@
         <v>14</v>
       </c>
       <c r="DZ92" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="93">
@@ -3962,7 +3968,7 @@
         <v>76</v>
       </c>
       <c r="C93" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CT93" t="s">
         <v>5</v>
@@ -3971,7 +3977,7 @@
         <v>9</v>
       </c>
       <c r="DU93" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="DZ93" t="s">
         <v>14</v>
@@ -3983,7 +3989,7 @@
         <v>14</v>
       </c>
       <c r="EC93" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="94">
@@ -3994,7 +4000,7 @@
         <v>80</v>
       </c>
       <c r="C94" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CT94" t="s">
         <v>5</v>
@@ -4003,13 +4009,13 @@
         <v>9</v>
       </c>
       <c r="DU94" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="EC94" t="s">
         <v>14</v>
       </c>
       <c r="ED94" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="95">
@@ -4020,7 +4026,7 @@
         <v>84</v>
       </c>
       <c r="C95" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="CU95" t="s">
         <v>5</v>
@@ -4029,16 +4035,16 @@
         <v>9</v>
       </c>
       <c r="DU95" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DV95" t="s">
         <v>14</v>
       </c>
       <c r="DW95" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="ED95" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="96">
@@ -4049,7 +4055,7 @@
         <v>88</v>
       </c>
       <c r="C96" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="CX96" t="s">
         <v>5</v>
@@ -4058,28 +4064,28 @@
         <v>9</v>
       </c>
       <c r="DV96" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DW96" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DX96" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DY96" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DZ96" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="EA96" t="s">
         <v>14</v>
       </c>
       <c r="EB96" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="ED96" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="97">
@@ -4090,7 +4096,7 @@
         <v>92</v>
       </c>
       <c r="C97" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="EB97" t="s">
         <v>5</v>
@@ -4108,7 +4114,7 @@
         <v>14</v>
       </c>
       <c r="EG97" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98">
@@ -4119,7 +4125,7 @@
         <v>96</v>
       </c>
       <c r="C98" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="EB98" t="s">
         <v>5</v>
@@ -4128,7 +4134,7 @@
         <v>9</v>
       </c>
       <c r="ED98" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="EG98" t="s">
         <v>14</v>
@@ -4140,7 +4146,7 @@
         <v>14</v>
       </c>
       <c r="EJ98" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="99">
@@ -4151,7 +4157,7 @@
         <v>100</v>
       </c>
       <c r="C99" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="EB99" t="s">
         <v>5</v>
@@ -4163,10 +4169,10 @@
         <v>14</v>
       </c>
       <c r="EE99" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="EJ99" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="100">
@@ -4177,7 +4183,7 @@
         <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="EB100" t="s">
         <v>5</v>
@@ -4186,10 +4192,10 @@
         <v>14</v>
       </c>
       <c r="EE100" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="EJ100" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="101">
@@ -4200,7 +4206,7 @@
         <v>108</v>
       </c>
       <c r="C101" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="EC101" t="s">
         <v>5</v>
@@ -4209,19 +4215,19 @@
         <v>9</v>
       </c>
       <c r="EE101" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="EF101" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="EG101" t="s">
         <v>14</v>
       </c>
       <c r="EH101" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="EJ101" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="102">
@@ -4232,7 +4238,7 @@
         <v>112</v>
       </c>
       <c r="C102" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="EC102" t="s">
         <v>5</v>
@@ -4241,19 +4247,19 @@
         <v>9</v>
       </c>
       <c r="EG102" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="EH102" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="EI102" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="EJ102" t="s">
         <v>14</v>
       </c>
       <c r="EK102" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="103">
@@ -4264,7 +4270,7 @@
         <v>116</v>
       </c>
       <c r="C103" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="EC103" t="s">
         <v>5</v>
@@ -4273,13 +4279,13 @@
         <v>9</v>
       </c>
       <c r="EJ103" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="EK103" t="s">
         <v>14</v>
       </c>
       <c r="EL103" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="104">
@@ -4290,7 +4296,7 @@
         <v>120</v>
       </c>
       <c r="C104" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="EC104" t="s">
         <v>5</v>
@@ -4299,16 +4305,16 @@
         <v>9</v>
       </c>
       <c r="EJ104" t="s">
+        <v>16</v>
+      </c>
+      <c r="EK104" t="s">
         <v>15</v>
       </c>
-      <c r="EK104" t="s">
-        <v>14</v>
-      </c>
       <c r="EL104" t="s">
         <v>14</v>
       </c>
       <c r="EM104" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="105">
@@ -4319,7 +4325,7 @@
         <v>124</v>
       </c>
       <c r="C105" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="ED105" t="s">
         <v>5</v>
@@ -4328,16 +4334,16 @@
         <v>9</v>
       </c>
       <c r="EK105" t="s">
+        <v>16</v>
+      </c>
+      <c r="EL105" t="s">
         <v>15</v>
       </c>
-      <c r="EL105" t="s">
-        <v>14</v>
-      </c>
       <c r="EM105" t="s">
         <v>14</v>
       </c>
       <c r="EN105" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="106">
@@ -4348,7 +4354,7 @@
         <v>128</v>
       </c>
       <c r="C106" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="ED106" t="s">
         <v>5</v>
@@ -4357,16 +4363,16 @@
         <v>9</v>
       </c>
       <c r="EL106" t="s">
+        <v>16</v>
+      </c>
+      <c r="EM106" t="s">
         <v>15</v>
       </c>
-      <c r="EM106" t="s">
-        <v>14</v>
-      </c>
       <c r="EN106" t="s">
         <v>14</v>
       </c>
       <c r="EO106" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="107">
@@ -4377,7 +4383,7 @@
         <v>132</v>
       </c>
       <c r="C107" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="ED107" t="s">
         <v>5</v>
@@ -4386,16 +4392,16 @@
         <v>9</v>
       </c>
       <c r="EM107" t="s">
+        <v>16</v>
+      </c>
+      <c r="EN107" t="s">
         <v>15</v>
       </c>
-      <c r="EN107" t="s">
-        <v>14</v>
-      </c>
       <c r="EO107" t="s">
         <v>14</v>
       </c>
       <c r="EP107" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="108">
@@ -4406,7 +4412,7 @@
         <v>136</v>
       </c>
       <c r="C108" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="ED108" t="s">
         <v>5</v>
@@ -4415,16 +4421,16 @@
         <v>9</v>
       </c>
       <c r="EN108" t="s">
+        <v>16</v>
+      </c>
+      <c r="EO108" t="s">
         <v>15</v>
       </c>
-      <c r="EO108" t="s">
-        <v>14</v>
-      </c>
       <c r="EP108" t="s">
         <v>14</v>
       </c>
       <c r="EQ108" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="109">
@@ -4435,7 +4441,7 @@
         <v>140</v>
       </c>
       <c r="C109" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="EE109" t="s">
         <v>5</v>
@@ -4444,21 +4450,21 @@
         <v>9</v>
       </c>
       <c r="EO109" t="s">
+        <v>16</v>
+      </c>
+      <c r="EP109" t="s">
         <v>15</v>
       </c>
-      <c r="EP109" t="s">
-        <v>14</v>
-      </c>
       <c r="EQ109" t="s">
         <v>14</v>
       </c>
       <c r="ER109" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="112">
@@ -4466,7 +4472,7 @@
         <v>5</v>
       </c>
       <c r="B112" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="113">
@@ -4474,15 +4480,15 @@
         <v>9</v>
       </c>
       <c r="B113" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B114" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="115">
@@ -4490,39 +4496,55 @@
         <v>14</v>
       </c>
       <c r="B115" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B116" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B117" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B118" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
+        <v>33</v>
+      </c>
+      <c r="B119" t="s">
         <v>56</v>
       </c>
-      <c r="B119" t="s">
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
         <v>57</v>
+      </c>
+      <c r="B120" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
